--- a/salidas/empresas/DVN.xlsx
+++ b/salidas/empresas/DVN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.41629409790039</v>
+        <v>41.41629791259766</v>
       </c>
       <c r="C2" t="n">
         <v>68.20999908447266</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.59945297241211</v>
+        <v>35.59944915771484</v>
       </c>
       <c r="C3" t="n">
         <v>58.63000106811523</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.21567916870117</v>
+        <v>37.21569442749023</v>
       </c>
       <c r="C4" t="n">
         <v>61.16999816894531</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>36.57080078125</v>
+        <v>36.57081604003906</v>
       </c>
       <c r="C5" t="n">
         <v>60.11000061035156</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>39.41262817382812</v>
+        <v>39.41263961791992</v>
       </c>
       <c r="C8" t="n">
         <v>64.63999938964844</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.10172653198242</v>
+        <v>38.10174942016602</v>
       </c>
       <c r="C9" t="n">
         <v>62.4900016784668</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>38.57099151611328</v>
+        <v>38.57099914550781</v>
       </c>
       <c r="C10" t="n">
         <v>63.15000152587891</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>40.82480621337891</v>
+        <v>40.82479476928711</v>
       </c>
       <c r="C11" t="n">
         <v>66.83999633789062</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>44.81320953369141</v>
+        <v>44.81321716308594</v>
       </c>
       <c r="C12" t="n">
         <v>73.37000274658203</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>41.03668975830078</v>
+        <v>41.03670120239258</v>
       </c>
       <c r="C13" t="n">
         <v>67.08000183105469</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.87806701660156</v>
+        <v>42.87807083129883</v>
       </c>
       <c r="C14" t="n">
         <v>70.08999633789062</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>40.19245529174805</v>
+        <v>40.19246673583984</v>
       </c>
       <c r="C15" t="n">
         <v>65.69999694824219</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.43818283081055</v>
+        <v>42.43818664550781</v>
       </c>
       <c r="C16" t="n">
         <v>69.22000122070312</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.67596435546875</v>
+        <v>44.67597961425781</v>
       </c>
       <c r="C17" t="n">
         <v>72.87000274658203</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>47.07313537597656</v>
+        <v>47.07314300537109</v>
       </c>
       <c r="C18" t="n">
         <v>76.77999877929688</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>48.08498001098633</v>
+        <v>48.08499526977539</v>
       </c>
       <c r="C19" t="n">
         <v>78.29000091552734</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>45.82477188110352</v>
+        <v>45.82477951049805</v>
       </c>
       <c r="C20" t="n">
         <v>74.61000061035156</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>46.25469970703125</v>
+        <v>46.25469207763672</v>
       </c>
       <c r="C21" t="n">
         <v>75.30999755859375</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>51.19191360473633</v>
+        <v>51.1919059753418</v>
       </c>
       <c r="C22" t="n">
         <v>83.19999694824219</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>57.46788024902344</v>
+        <v>57.46783828735352</v>
       </c>
       <c r="C23" t="n">
         <v>93.40000152587891</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>50.95195007324219</v>
+        <v>50.95195770263672</v>
       </c>
       <c r="C24" t="n">
         <v>82.80999755859375</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>54.79340744018555</v>
+        <v>54.79338836669922</v>
       </c>
       <c r="C25" t="n">
         <v>88.91000366210938</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>52.41455841064453</v>
+        <v>52.41460037231445</v>
       </c>
       <c r="C26" t="n">
         <v>85.05000305175781</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>63.30421447753906</v>
+        <v>63.30423355102539</v>
       </c>
       <c r="C27" t="n">
         <v>102.7200012207031</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>64.49668884277344</v>
+        <v>64.4967041015625</v>
       </c>
       <c r="C28" t="n">
         <v>104.3300018310547</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>71.67401123046875</v>
+        <v>71.67398834228516</v>
       </c>
       <c r="C30" t="n">
         <v>115.9400024414062</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>74.3848876953125</v>
+        <v>74.38486480712891</v>
       </c>
       <c r="C31" t="n">
         <v>120.1600036621094</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>58.74150848388672</v>
+        <v>58.74152374267578</v>
       </c>
       <c r="C32" t="n">
         <v>94.88999938964844</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>56.55511856079102</v>
+        <v>56.55510711669922</v>
       </c>
       <c r="C34" t="n">
         <v>91.19999694824219</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>50.1430778503418</v>
+        <v>50.1430549621582</v>
       </c>
       <c r="C35" t="n">
         <v>80.86000061035156</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>44.85961532592773</v>
+        <v>44.85962295532227</v>
       </c>
       <c r="C36" t="n">
         <v>72.33999633789062</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>40.83825302124023</v>
+        <v>40.83826446533203</v>
       </c>
       <c r="C37" t="n">
         <v>65.70999908447266</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>38.28391647338867</v>
+        <v>38.28393173217773</v>
       </c>
       <c r="C38" t="n">
         <v>61.59999847412109</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>27.14057540893555</v>
+        <v>27.14057159423828</v>
       </c>
       <c r="C39" t="n">
         <v>43.66999816894531</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.87994575500488</v>
+        <v>27.87995338439941</v>
       </c>
       <c r="C40" t="n">
         <v>44.68999862670898</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.34672927856445</v>
+        <v>32.34674835205078</v>
       </c>
       <c r="C41" t="n">
         <v>51.84999847412109</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>39.45240020751953</v>
+        <v>39.45241546630859</v>
       </c>
       <c r="C42" t="n">
         <v>63.2400016784668</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>34.08547973632812</v>
+        <v>34.08549118041992</v>
       </c>
       <c r="C43" t="n">
         <v>54.5</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>36.33075714111328</v>
+        <v>36.33074188232422</v>
       </c>
       <c r="C44" t="n">
         <v>58.09000015258789</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>38.38839340209961</v>
+        <v>38.38838195800781</v>
       </c>
       <c r="C45" t="n">
         <v>61.38000106811523</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>42.21286010742188</v>
+        <v>42.21286773681641</v>
       </c>
       <c r="C46" t="n">
         <v>67.33000183105469</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>40.57024002075195</v>
+        <v>40.57025909423828</v>
       </c>
       <c r="C47" t="n">
         <v>64.70999908447266</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>42.22540664672852</v>
+        <v>42.22539901733398</v>
       </c>
       <c r="C48" t="n">
         <v>67.34999847412109</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>46.19659423828125</v>
+        <v>46.19659805297852</v>
       </c>
       <c r="C49" t="n">
         <v>73.5</v>
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>43.28022766113281</v>
+        <v>43.28025436401367</v>
       </c>
       <c r="C51" t="n">
         <v>68.86000061035156</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>40.58625793457031</v>
+        <v>40.58625030517578</v>
       </c>
       <c r="C52" t="n">
         <v>64.43000030517578</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>42.41304016113281</v>
+        <v>42.41305923461914</v>
       </c>
       <c r="C53" t="n">
         <v>67.33000183105469</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>40.22089004516602</v>
+        <v>40.22089767456055</v>
       </c>
       <c r="C54" t="n">
         <v>63.84999847412109</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>38.46593856811523</v>
+        <v>38.46595001220703</v>
       </c>
       <c r="C55" t="n">
         <v>60.91999816894531</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>38.06183242797852</v>
+        <v>38.06183624267578</v>
       </c>
       <c r="C57" t="n">
         <v>60.27999877929688</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>40.98283004760742</v>
+        <v>40.98282241821289</v>
       </c>
       <c r="C58" t="n">
         <v>64.73999786376953</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>41.16006088256836</v>
+        <v>41.16008377075195</v>
       </c>
       <c r="C59" t="n">
         <v>65.01999664306641</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>44.67343902587891</v>
+        <v>44.67343521118164</v>
       </c>
       <c r="C60" t="n">
         <v>70.56999969482422</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>49.8084716796875</v>
+        <v>49.80847930908203</v>
       </c>
       <c r="C61" t="n">
         <v>78.51000213623047</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>56.26689529418945</v>
+        <v>56.26690673828125</v>
       </c>
       <c r="C62" t="n">
         <v>88.69000244140625</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>58.01158905029297</v>
+        <v>58.01158142089844</v>
       </c>
       <c r="C63" t="n">
         <v>91.44000244140625</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>58.32935333251953</v>
+        <v>58.32931900024414</v>
       </c>
       <c r="C64" t="n">
         <v>91.76999664306641</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>57.83990097045898</v>
+        <v>57.83990859985352</v>
       </c>
       <c r="C65" t="n">
         <v>91</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>53.43520736694336</v>
+        <v>53.4351921081543</v>
       </c>
       <c r="C66" t="n">
         <v>84.06999969482422</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>50.19921112060547</v>
+        <v>50.19922256469727</v>
       </c>
       <c r="C67" t="n">
         <v>78.80999755859375</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>50.12914276123047</v>
+        <v>50.129150390625</v>
       </c>
       <c r="C68" t="n">
         <v>78.69999694824219</v>
@@ -1923,7 +1935,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>35.40772247314453</v>
+        <v>35.40771865844727</v>
       </c>
       <c r="C70" t="n">
         <v>55.43999862670898</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.48143005371094</v>
+        <v>41.48145294189453</v>
       </c>
       <c r="C71" t="n">
         <v>64.94999694824219</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>41.80715560913086</v>
+        <v>41.80717849731445</v>
       </c>
       <c r="C72" t="n">
         <v>65.45999908447266</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>39.70246124267578</v>
+        <v>39.70245742797852</v>
       </c>
       <c r="C73" t="n">
         <v>62</v>
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>46.9449577331543</v>
+        <v>46.94495391845703</v>
       </c>
       <c r="C75" t="n">
         <v>73.30999755859375</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>45.67101287841797</v>
+        <v>45.67102432250977</v>
       </c>
       <c r="C76" t="n">
         <v>71.12000274658203</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>44.85546493530273</v>
+        <v>44.85546875</v>
       </c>
       <c r="C77" t="n">
         <v>69.84999847412109</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>38.22187805175781</v>
+        <v>38.22187042236328</v>
       </c>
       <c r="C78" t="n">
         <v>59.52000045776367</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>37.36922073364258</v>
+        <v>37.36921691894531</v>
       </c>
       <c r="C79" t="n">
         <v>57.9900016784668</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>38.09740447998047</v>
+        <v>38.09739303588867</v>
       </c>
       <c r="C80" t="n">
         <v>59.11999893188477</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>37.26610946655273</v>
+        <v>37.26611328125</v>
       </c>
       <c r="C81" t="n">
         <v>57.83000183105469</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>39.11573028564453</v>
+        <v>39.11572647094727</v>
       </c>
       <c r="C82" t="n">
         <v>60.5</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>37.63514709472656</v>
+        <v>37.63515472412109</v>
       </c>
       <c r="C83" t="n">
         <v>58.20999908447266</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>33.40677642822266</v>
+        <v>33.40676498413086</v>
       </c>
       <c r="C84" t="n">
         <v>51.66999816894531</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>33.77476501464844</v>
+        <v>33.77476119995117</v>
       </c>
       <c r="C85" t="n">
         <v>52.04000091552734</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>37.11719131469727</v>
+        <v>37.1171875</v>
       </c>
       <c r="C86" t="n">
         <v>57.18999862670898</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>35.21558380126953</v>
+        <v>35.2155647277832</v>
       </c>
       <c r="C87" t="n">
         <v>54.2599983215332</v>
@@ -2472,11 +2484,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>36.7490234375</v>
+        <v>36.74901962280273</v>
       </c>
       <c r="C88" t="n">
         <v>56.41999816894531</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>35.86319351196289</v>
+        <v>35.86318588256836</v>
       </c>
       <c r="C89" t="n">
         <v>55.06000137329102</v>
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>37.02910232543945</v>
+        <v>37.02909851074219</v>
       </c>
       <c r="C90" t="n">
         <v>56.84999847412109</v>
@@ -2553,11 +2565,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>33.92697525024414</v>
+        <v>33.92696762084961</v>
       </c>
       <c r="C91" t="n">
         <v>51.88000106811523</v>
@@ -2580,11 +2592,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>35.97384262084961</v>
+        <v>35.97383880615234</v>
       </c>
       <c r="C92" t="n">
         <v>55.0099983215332</v>
@@ -2607,11 +2619,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.33405303955078</v>
+        <v>37.33406066894531</v>
       </c>
       <c r="C93" t="n">
         <v>57.09000015258789</v>
@@ -2634,11 +2646,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>37.91429138183594</v>
+        <v>37.9142951965332</v>
       </c>
       <c r="C94" t="n">
         <v>57.7599983215332</v>
@@ -2661,7 +2673,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>39.79163360595703</v>
+        <v>39.79162216186523</v>
       </c>
       <c r="C96" t="n">
         <v>60.61999893188477</v>
@@ -2715,7 +2727,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2742,7 +2754,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2769,11 +2781,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>42.43951797485352</v>
+        <v>42.43949890136719</v>
       </c>
       <c r="C99" t="n">
         <v>64.41999816894531</v>
@@ -2796,11 +2808,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>44.24626159667969</v>
+        <v>44.24625778198242</v>
       </c>
       <c r="C100" t="n">
         <v>66.93000030517578</v>
@@ -2823,11 +2835,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>46.27577590942383</v>
+        <v>46.27579498291016</v>
       </c>
       <c r="C101" t="n">
         <v>70</v>
@@ -2850,11 +2862,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.8540153503418</v>
+        <v>48.85400009155273</v>
       </c>
       <c r="C102" t="n">
         <v>73.90000152587891</v>
@@ -2879,11 +2891,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>52.65859603881836</v>
+        <v>52.65860366821289</v>
       </c>
       <c r="C103" t="n">
         <v>79.40000152587891</v>
@@ -2908,11 +2920,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>50.07209777832031</v>
+        <v>50.07209396362305</v>
       </c>
       <c r="C104" t="n">
         <v>75.5</v>
@@ -2937,7 +2949,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2966,11 +2978,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.37133407592773</v>
+        <v>45.37134170532227</v>
       </c>
       <c r="C106" t="n">
         <v>68.18000030517578</v>
@@ -2995,11 +3007,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.9278450012207</v>
+        <v>39.92783355712891</v>
       </c>
       <c r="C107" t="n">
         <v>60</v>
@@ -3024,11 +3036,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.24241638183594</v>
+        <v>39.24240875244141</v>
       </c>
       <c r="C108" t="n">
         <v>58.97000122070312</v>
@@ -3053,11 +3065,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>40.90467834472656</v>
+        <v>40.90468597412109</v>
       </c>
       <c r="C109" t="n">
         <v>61.20999908447266</v>
@@ -3082,7 +3094,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3111,11 +3123,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>41.15862274169922</v>
+        <v>41.15861511230469</v>
       </c>
       <c r="C111" t="n">
         <v>61.59000015258789</v>
@@ -3140,11 +3152,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>40.47369384765625</v>
+        <v>40.47367858886719</v>
       </c>
       <c r="C112" t="n">
         <v>60.31000137329102</v>
@@ -3169,11 +3181,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>45.77532196044922</v>
+        <v>45.77531814575195</v>
       </c>
       <c r="C113" t="n">
         <v>68.20999908447266</v>
@@ -3198,11 +3210,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>43.76875686645508</v>
+        <v>43.76876068115234</v>
       </c>
       <c r="C114" t="n">
         <v>65.22000122070312</v>
@@ -3225,7 +3237,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3252,11 +3264,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.29068374633789</v>
+        <v>33.29067993164062</v>
       </c>
       <c r="C116" t="n">
         <v>49.41999816894531</v>
@@ -3279,11 +3291,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>28.73695373535156</v>
+        <v>28.73696136474609</v>
       </c>
       <c r="C117" t="n">
         <v>42.65999984741211</v>
@@ -3306,11 +3318,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>25.13569259643555</v>
+        <v>25.13569831848145</v>
       </c>
       <c r="C118" t="n">
         <v>37.09000015258789</v>
@@ -3333,11 +3345,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>28.41575050354004</v>
+        <v>28.41574096679688</v>
       </c>
       <c r="C119" t="n">
         <v>41.93000030517578</v>
@@ -3360,7 +3372,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3387,11 +3399,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>21.83380126953125</v>
+        <v>21.83380317687988</v>
       </c>
       <c r="C121" t="n">
         <v>32</v>
@@ -3414,7 +3426,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3441,7 +3453,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3468,11 +3480,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>18.92452812194824</v>
+        <v>18.92452621459961</v>
       </c>
       <c r="C124" t="n">
         <v>27.44000053405762</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>23.91772651672363</v>
+        <v>23.9177303314209</v>
       </c>
       <c r="C125" t="n">
         <v>34.68000030517578</v>
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3549,11 +3561,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.04329490661621</v>
+        <v>25.04329681396484</v>
       </c>
       <c r="C127" t="n">
         <v>36.25</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>26.44572448730469</v>
+        <v>26.44571876525879</v>
       </c>
       <c r="C128" t="n">
         <v>38.27999877929688</v>
@@ -3603,7 +3615,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.51576232910156</v>
+        <v>30.51577377319336</v>
       </c>
       <c r="C130" t="n">
         <v>44.11000061035156</v>
@@ -3657,11 +3669,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>26.21270942687988</v>
+        <v>26.21270179748535</v>
       </c>
       <c r="C131" t="n">
         <v>37.88999938964844</v>
@@ -3684,11 +3696,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>33.43521118164062</v>
+        <v>33.43521499633789</v>
       </c>
       <c r="C132" t="n">
         <v>48.33000183105469</v>
@@ -3711,11 +3723,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>31.63442993164062</v>
+        <v>31.63443756103516</v>
       </c>
       <c r="C133" t="n">
         <v>45.66999816894531</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>31.54440116882324</v>
+        <v>31.54439163208008</v>
       </c>
       <c r="C134" t="n">
         <v>45.54000091552734</v>
@@ -3765,11 +3777,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>30.03436851501465</v>
+        <v>30.03436088562012</v>
       </c>
       <c r="C135" t="n">
         <v>43.36000061035156</v>
@@ -3792,11 +3804,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>28.94150161743164</v>
+        <v>28.94149971008301</v>
       </c>
       <c r="C136" t="n">
         <v>41.72000122070312</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>27.39453125</v>
+        <v>27.39453506469727</v>
       </c>
       <c r="C137" t="n">
         <v>39.4900016784668</v>
@@ -3846,11 +3858,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>23.57219886779785</v>
+        <v>23.57220268249512</v>
       </c>
       <c r="C138" t="n">
         <v>33.97999954223633</v>
@@ -3875,11 +3887,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>22.21859550476074</v>
+        <v>22.21859359741211</v>
       </c>
       <c r="C139" t="n">
         <v>31.96999931335449</v>
@@ -3904,7 +3916,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3933,7 +3945,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -3962,11 +3974,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>25.55857276916504</v>
+        <v>25.55856704711914</v>
       </c>
       <c r="C142" t="n">
         <v>36.70999908447266</v>
@@ -3991,11 +4003,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>25.69084930419922</v>
+        <v>25.69086456298828</v>
       </c>
       <c r="C143" t="n">
         <v>36.90000152587891</v>
@@ -4020,11 +4032,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>26.82570457458496</v>
+        <v>26.82571029663086</v>
       </c>
       <c r="C144" t="n">
         <v>38.52999877929688</v>
@@ -4049,11 +4061,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>28.86933708190918</v>
+        <v>28.86932373046875</v>
       </c>
       <c r="C145" t="n">
         <v>41.40000152587891</v>
@@ -4078,11 +4090,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>28.84840965270996</v>
+        <v>28.84840202331543</v>
       </c>
       <c r="C146" t="n">
         <v>41.36999893188477</v>
@@ -4107,11 +4119,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>21.38701248168945</v>
+        <v>21.38701438903809</v>
       </c>
       <c r="C147" t="n">
         <v>30.67000007629395</v>
@@ -4136,11 +4148,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>22.20865249633789</v>
+        <v>22.20866203308105</v>
       </c>
       <c r="C148" t="n">
         <v>31.79000091552734</v>
@@ -4165,7 +4177,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4194,11 +4206,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>29.04101943969727</v>
+        <v>29.041015625</v>
       </c>
       <c r="C150" t="n">
         <v>41.56999969482422</v>
@@ -4223,11 +4235,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>30.76847267150879</v>
+        <v>30.76847076416016</v>
       </c>
       <c r="C151" t="n">
         <v>43.95999908447266</v>
@@ -4252,11 +4264,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>31.50339126586914</v>
+        <v>31.50338745117188</v>
       </c>
       <c r="C152" t="n">
         <v>45.0099983215332</v>
@@ -4281,11 +4293,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>30.04756164550781</v>
+        <v>30.04755020141602</v>
       </c>
       <c r="C153" t="n">
         <v>42.93000030517578</v>
@@ -4308,11 +4320,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>28.00820541381836</v>
+        <v>28.00821113586426</v>
       </c>
       <c r="C154" t="n">
         <v>39.93999862670898</v>
@@ -4335,11 +4347,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>22.72073364257812</v>
+        <v>22.72073554992676</v>
       </c>
       <c r="C155" t="n">
         <v>32.40000152587891</v>
@@ -4362,11 +4374,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>18.95498275756836</v>
+        <v>18.95497894287109</v>
       </c>
       <c r="C156" t="n">
         <v>27.03000068664551</v>
@@ -4391,7 +4403,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4420,11 +4432,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>18.74346923828125</v>
+        <v>18.74347114562988</v>
       </c>
       <c r="C158" t="n">
         <v>26.64999961853027</v>
@@ -4449,7 +4461,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4478,11 +4490,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>22.25747680664062</v>
+        <v>22.25747299194336</v>
       </c>
       <c r="C160" t="n">
         <v>31.55999946594238</v>
@@ -4507,11 +4519,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>22.66651725769043</v>
+        <v>22.66651344299316</v>
       </c>
       <c r="C161" t="n">
         <v>32.13999938964844</v>
@@ -4536,7 +4548,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4565,7 +4577,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4594,11 +4606,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>19.10906600952148</v>
+        <v>19.10906028747559</v>
       </c>
       <c r="C164" t="n">
         <v>27</v>
@@ -4623,11 +4635,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>15.56327152252197</v>
+        <v>15.56327342987061</v>
       </c>
       <c r="C165" t="n">
         <v>21.98999977111816</v>
@@ -4652,11 +4664,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>17.08989715576172</v>
+        <v>17.08990097045898</v>
       </c>
       <c r="C166" t="n">
         <v>24.05999946594238</v>
@@ -4681,11 +4693,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>14.40495014190674</v>
+        <v>14.40495204925537</v>
       </c>
       <c r="C167" t="n">
         <v>20.28000068664551</v>
@@ -4710,11 +4722,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>15.54854106903076</v>
+        <v>15.54853534698486</v>
       </c>
       <c r="C168" t="n">
         <v>21.88999938964844</v>
@@ -4739,11 +4751,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>18.51773643493652</v>
+        <v>18.51773452758789</v>
       </c>
       <c r="C169" t="n">
         <v>25.96999931335449</v>
@@ -4768,11 +4780,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>15.48730278015137</v>
+        <v>15.48730182647705</v>
       </c>
       <c r="C170" t="n">
         <v>21.71999931335449</v>
@@ -4797,11 +4809,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>11.57982540130615</v>
+        <v>11.57982635498047</v>
       </c>
       <c r="C171" t="n">
         <v>16.23999977111816</v>
@@ -4824,7 +4836,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4851,11 +4863,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>8.987835884094238</v>
+        <v>8.987834930419922</v>
       </c>
       <c r="C173" t="n">
         <v>12.47000026702881</v>
@@ -4878,11 +4890,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>7.791379928588867</v>
+        <v>7.791380882263184</v>
       </c>
       <c r="C174" t="n">
         <v>10.8100004196167</v>
@@ -4905,11 +4917,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>8.247747421264648</v>
+        <v>8.247745513916016</v>
       </c>
       <c r="C175" t="n">
         <v>11.34000015258789</v>
@@ -4932,11 +4944,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>7.62952709197998</v>
+        <v>7.629529476165771</v>
       </c>
       <c r="C176" t="n">
         <v>10.48999977111816</v>
@@ -4959,7 +4971,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4986,7 +4998,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5013,11 +5025,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>6.716057777404785</v>
+        <v>6.716056823730469</v>
       </c>
       <c r="C179" t="n">
         <v>8.930000305175781</v>
@@ -5040,11 +5052,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>10.52157402038574</v>
+        <v>10.52157115936279</v>
       </c>
       <c r="C180" t="n">
         <v>13.98999977111816</v>
@@ -5067,11 +5079,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>11.97419738769531</v>
+        <v>11.974196434021</v>
       </c>
       <c r="C181" t="n">
         <v>15.8100004196167</v>
@@ -5094,7 +5106,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5121,11 +5133,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>16.31399154663086</v>
+        <v>16.31398963928223</v>
       </c>
       <c r="C183" t="n">
         <v>21.54000091552734</v>
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>16.75275230407715</v>
+        <v>16.75274467468262</v>
       </c>
       <c r="C184" t="n">
         <v>21.85000038146973</v>
@@ -5175,7 +5187,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5202,11 +5214,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>20.36398315429688</v>
+        <v>20.36397552490234</v>
       </c>
       <c r="C186" t="n">
         <v>26.55999946594238</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>22.64238739013672</v>
+        <v>22.64238548278809</v>
       </c>
       <c r="C187" t="n">
         <v>29.19000053405762</v>
@@ -5256,11 +5268,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>20.0438232421875</v>
+        <v>20.0438289642334</v>
       </c>
       <c r="C188" t="n">
         <v>25.84000015258789</v>
@@ -5283,11 +5295,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>22.92163467407227</v>
+        <v>22.921630859375</v>
       </c>
       <c r="C189" t="n">
         <v>29.54999923706055</v>
@@ -5312,11 +5324,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>28.02746391296387</v>
+        <v>28.02746200561523</v>
       </c>
       <c r="C190" t="n">
         <v>35.5099983215332</v>
@@ -5341,11 +5353,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.63449859619141</v>
+        <v>31.63449668884277</v>
       </c>
       <c r="C191" t="n">
         <v>40.08000183105469</v>
@@ -5370,7 +5382,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5399,11 +5411,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43064880371094</v>
+        <v>35.43064498901367</v>
       </c>
       <c r="C193" t="n">
         <v>44.04999923706055</v>
@@ -5428,11 +5440,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>40.67486190795898</v>
+        <v>40.67486572265625</v>
       </c>
       <c r="C194" t="n">
         <v>50.56999969482422</v>
@@ -5457,11 +5469,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>47.89773178100586</v>
+        <v>47.89772415161133</v>
       </c>
       <c r="C195" t="n">
         <v>59.54999923706055</v>
@@ -5486,11 +5498,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>48.35829925537109</v>
+        <v>48.35830307006836</v>
       </c>
       <c r="C196" t="n">
         <v>59.13000106811523</v>
@@ -5515,7 +5527,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5544,11 +5556,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>61.25550079345703</v>
+        <v>61.2554817199707</v>
       </c>
       <c r="C198" t="n">
         <v>74.90000152587891</v>
@@ -5573,7 +5585,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5602,11 +5614,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>52.2530517578125</v>
+        <v>52.25305557250977</v>
       </c>
       <c r="C200" t="n">
         <v>62.84999847412109</v>
@@ -5631,11 +5643,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>58.71297454833984</v>
+        <v>58.71298217773438</v>
       </c>
       <c r="C201" t="n">
         <v>70.62000274658203</v>
@@ -5660,11 +5672,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>51.14200592041016</v>
+        <v>51.14200210571289</v>
       </c>
       <c r="C202" t="n">
         <v>60.13000106811523</v>
@@ -5689,11 +5701,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>65.78804016113281</v>
+        <v>65.78803253173828</v>
       </c>
       <c r="C203" t="n">
         <v>77.34999847412109</v>
@@ -5718,11 +5730,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>58.27790069580078</v>
+        <v>58.27790832519531</v>
       </c>
       <c r="C204" t="n">
         <v>68.51999664306641</v>
@@ -5747,11 +5759,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>53.45211410522461</v>
+        <v>53.45212173461914</v>
       </c>
       <c r="C205" t="n">
         <v>61.5099983215332</v>
@@ -5776,11 +5788,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>54.95548629760742</v>
+        <v>54.95548248291016</v>
       </c>
       <c r="C206" t="n">
         <v>63.2400016784668</v>
@@ -5805,11 +5817,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.85641479492188</v>
+        <v>46.85641098022461</v>
       </c>
       <c r="C207" t="n">
         <v>53.91999816894531</v>
@@ -5834,11 +5846,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>44.77738952636719</v>
+        <v>44.77738571166992</v>
       </c>
       <c r="C208" t="n">
         <v>50.61000061035156</v>
@@ -5863,11 +5875,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>47.27239608764648</v>
+        <v>47.27239227294922</v>
       </c>
       <c r="C209" t="n">
         <v>53.43000030517578</v>
@@ -5892,11 +5904,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>40.78714752197266</v>
+        <v>40.78715515136719</v>
       </c>
       <c r="C210" t="n">
         <v>46.09999847412109</v>
@@ -5921,11 +5933,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>43.38895416259766</v>
+        <v>43.38896942138672</v>
       </c>
       <c r="C211" t="n">
         <v>48.34000015258789</v>
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5979,11 +5991,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>45.85729598999023</v>
+        <v>45.85730361938477</v>
       </c>
       <c r="C213" t="n">
         <v>51.09000015258789</v>
@@ -6008,7 +6020,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6037,11 +6049,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>42.20858383178711</v>
+        <v>42.20858001708984</v>
       </c>
       <c r="C215" t="n">
         <v>46.56999969482422</v>
@@ -6066,7 +6078,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6095,11 +6107,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>41.78512191772461</v>
+        <v>41.78512954711914</v>
       </c>
       <c r="C217" t="n">
         <v>45.29999923706055</v>
@@ -6124,11 +6136,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>38.75962829589844</v>
+        <v>38.75962066650391</v>
       </c>
       <c r="C218" t="n">
         <v>42.02000045776367</v>
@@ -6153,11 +6165,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>40.64133453369141</v>
+        <v>40.64134216308594</v>
       </c>
       <c r="C219" t="n">
         <v>44.06000137329102</v>
@@ -6182,11 +6194,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>46.72007751464844</v>
+        <v>46.72006988525391</v>
       </c>
       <c r="C220" t="n">
         <v>50.18000030517578</v>
@@ -6211,11 +6223,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>47.651123046875</v>
+        <v>47.65113067626953</v>
       </c>
       <c r="C221" t="n">
         <v>51.18000030517578</v>
@@ -6240,11 +6252,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>45.6959228515625</v>
+        <v>45.69591522216797</v>
       </c>
       <c r="C222" t="n">
         <v>49.08000183105469</v>
@@ -6269,11 +6281,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.47190856933594</v>
+        <v>44.47190475463867</v>
       </c>
       <c r="C223" t="n">
         <v>47.40000152587891</v>
@@ -6298,7 +6310,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6327,7 +6339,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6356,7 +6368,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6385,7 +6397,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6414,11 +6426,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>36.00159454345703</v>
+        <v>36.0015869140625</v>
       </c>
       <c r="C228" t="n">
         <v>37.95000076293945</v>
@@ -6443,11 +6455,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>31.25103187561035</v>
+        <v>31.25103378295898</v>
       </c>
       <c r="C229" t="n">
         <v>32.72999954223633</v>
@@ -6472,7 +6484,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6501,11 +6513,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>34.58333206176758</v>
+        <v>34.58333969116211</v>
       </c>
       <c r="C231" t="n">
         <v>36.22000122070312</v>
@@ -6530,11 +6542,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>35.9654655456543</v>
+        <v>35.96546173095703</v>
       </c>
       <c r="C232" t="n">
         <v>37.40000152587891</v>
@@ -6559,11 +6571,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>29.24357414245605</v>
+        <v>29.24357223510742</v>
       </c>
       <c r="C233" t="n">
         <v>30.40999984741211</v>
@@ -6588,7 +6600,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6617,7 +6629,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6646,11 +6658,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>32.17070007324219</v>
+        <v>32.17069625854492</v>
       </c>
       <c r="C236" t="n">
         <v>33.22000122070312</v>
@@ -6675,11 +6687,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>34.95972442626953</v>
+        <v>34.9597282409668</v>
       </c>
       <c r="C237" t="n">
         <v>36.09999847412109</v>
@@ -6704,11 +6716,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>34.18857192993164</v>
+        <v>34.18856811523438</v>
       </c>
       <c r="C238" t="n">
         <v>35.06000137329102</v>
@@ -6733,11 +6745,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>31.68244743347168</v>
+        <v>31.68244552612305</v>
       </c>
       <c r="C239" t="n">
         <v>32.4900016784668</v>
@@ -6762,7 +6774,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6791,7 +6803,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6820,7 +6832,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6849,11 +6861,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>42.72130584716797</v>
+        <v>42.72130966186523</v>
       </c>
       <c r="C243" t="n">
         <v>43.52999877929688</v>
@@ -6878,7 +6890,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6907,7 +6919,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6936,7 +6948,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6965,7 +6977,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6994,7 +7006,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7023,7 +7035,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7052,32 +7064,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>48.04000091552734</v>
+        <v>48.90000152587891</v>
       </c>
       <c r="C250" t="n">
-        <v>48.04000091552734</v>
+        <v>48.90000152587891</v>
       </c>
       <c r="D250" t="n">
-        <v>216076400</v>
+        <v>233663700</v>
       </c>
       <c r="E250" t="n">
         <v>4.210000000000004</v>
       </c>
       <c r="F250" t="n">
-        <v>11.41092658326064</v>
+        <v>11.61520226267906</v>
       </c>
       <c r="G250" t="n">
         <v>1100000000</v>
       </c>
       <c r="H250" t="n">
-        <v>52844001007.08008</v>
+        <v>53790001678.4668</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1964330909090909</v>
+        <v>0.2124215454545454</v>
       </c>
     </row>
   </sheetData>
@@ -7109,75 +7121,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7213,13 +7225,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7255,13 +7267,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7297,13 +7309,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7414,7 +7426,7 @@
       <c r="I7" t="n">
         <v>-5.609999999999999</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7427,13 +7439,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7460,7 +7472,7 @@
       <c r="I8" t="n">
         <v>5.970000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7473,13 +7485,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7506,7 +7518,7 @@
       <c r="I9" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7519,13 +7531,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7552,7 +7564,7 @@
       <c r="I10" t="n">
         <v>10.52</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7565,13 +7577,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="I11" t="n">
         <v>10.32</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7611,13 +7623,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7644,7 +7656,7 @@
       <c r="I12" t="n">
         <v>8.630000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K12" t="n">
@@ -7657,13 +7669,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7690,7 +7702,7 @@
       <c r="I13" t="n">
         <v>13.53</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K13" t="n">
@@ -7703,13 +7715,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7736,7 +7748,7 @@
       <c r="I14" t="n">
         <v>11.24</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7749,13 +7761,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7782,7 +7794,7 @@
       <c r="I15" t="n">
         <v>11.2</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7795,13 +7807,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7828,7 +7840,7 @@
       <c r="I16" t="n">
         <v>11.2</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7841,13 +7853,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7874,7 +7886,7 @@
       <c r="I17" t="n">
         <v>5.9</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K17" t="n">
@@ -7887,13 +7899,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7920,7 +7932,7 @@
       <c r="I18" t="n">
         <v>1.600000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K18" t="n">
@@ -7933,13 +7945,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7966,7 +7978,7 @@
       <c r="I19" t="n">
         <v>-0.5399999999999993</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K19" t="n">
@@ -7979,13 +7991,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8012,7 +8024,7 @@
       <c r="I20" t="n">
         <v>-4.85</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8025,13 +8037,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8058,7 +8070,7 @@
       <c r="I21" t="n">
         <v>-4.349999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K21" t="n">
@@ -8071,13 +8083,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8104,7 +8116,7 @@
       <c r="I22" t="n">
         <v>-1.499999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K22" t="n">
@@ -8117,13 +8129,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8150,7 +8162,7 @@
       <c r="I23" t="n">
         <v>-0.09999999999999887</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K23" t="n">
@@ -8163,13 +8175,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8196,7 +8208,7 @@
       <c r="I24" t="n">
         <v>4.030000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="K24" t="n">
@@ -8209,13 +8221,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8242,7 +8254,7 @@
       <c r="I25" t="n">
         <v>3.990000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K25" t="n">
@@ -8255,13 +8267,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8288,7 +8300,7 @@
       <c r="I26" t="n">
         <v>5.410000000000002</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K26" t="n">
@@ -8301,13 +8313,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8334,7 +8346,7 @@
       <c r="I27" t="n">
         <v>3.890000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K27" t="n">
@@ -8347,13 +8359,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8380,7 +8392,7 @@
       <c r="I28" t="n">
         <v>-5.779999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K28" t="n">
@@ -8393,13 +8405,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8426,7 +8438,7 @@
       <c r="I29" t="n">
         <v>-14.36</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K29" t="n">
@@ -8439,13 +8451,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8472,7 +8484,7 @@
       <c r="I30" t="n">
         <v>-25.47</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8485,13 +8497,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8518,7 +8530,7 @@
       <c r="I31" t="n">
         <v>-35.58</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="K31" t="n">
@@ -8531,13 +8543,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8564,7 +8576,7 @@
       <c r="I32" t="n">
         <v>-33.14</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K32" t="n">
@@ -8577,13 +8589,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8610,7 +8622,7 @@
       <c r="I33" t="n">
         <v>-29.23999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8623,13 +8635,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8656,7 +8668,7 @@
       <c r="I34" t="n">
         <v>-18.71</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K34" t="n">
@@ -8669,13 +8681,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8702,7 +8714,7 @@
       <c r="I35" t="n">
         <v>-6.959999999999997</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="K35" t="n">
@@ -8715,13 +8727,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8748,7 +8760,7 @@
       <c r="I36" t="n">
         <v>0.5500000000000034</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8761,13 +8773,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8794,7 +8806,7 @@
       <c r="I37" t="n">
         <v>4.390000000000003</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8807,13 +8819,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8840,7 +8852,7 @@
       <c r="I38" t="n">
         <v>2.930000000000004</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K38" t="n">
@@ -8853,13 +8865,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8886,7 +8898,7 @@
       <c r="I39" t="n">
         <v>1.700000000000003</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="K39" t="n">
@@ -8899,13 +8911,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8932,7 +8944,7 @@
       <c r="I40" t="n">
         <v>0.2500000000000032</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -8945,13 +8957,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8978,7 +8990,7 @@
       <c r="I41" t="n">
         <v>-1.379999999999997</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K41" t="n">
@@ -8991,13 +9003,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9024,7 +9036,7 @@
       <c r="I42" t="n">
         <v>3.330000000000003</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K42" t="n">
@@ -9037,13 +9049,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9070,7 +9082,7 @@
       <c r="I43" t="n">
         <v>6.410000000000004</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="K43" t="n">
@@ -9083,13 +9095,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9116,7 +9128,7 @@
       <c r="I44" t="n">
         <v>6.050000000000003</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9129,13 +9141,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9162,7 +9174,7 @@
       <c r="I45" t="n">
         <v>8.070000000000004</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K45" t="n">
@@ -9175,13 +9187,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9208,7 +9220,7 @@
       <c r="I46" t="n">
         <v>3.200000000000004</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K46" t="n">
@@ -9221,13 +9233,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9254,7 +9266,7 @@
       <c r="I47" t="n">
         <v>-0.9799999999999964</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K47" t="n">
@@ -9267,13 +9279,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9300,7 +9312,7 @@
       <c r="I48" t="n">
         <v>-5.059999999999997</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9313,13 +9325,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9346,7 +9358,7 @@
       <c r="I49" t="n">
         <v>-8.029999999999996</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9359,13 +9371,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9392,7 +9404,7 @@
       <c r="I50" t="n">
         <v>-8.549999999999997</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K50" t="n">
@@ -9405,13 +9417,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9438,7 +9450,7 @@
       <c r="I51" t="n">
         <v>-7.119999999999997</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="K51" t="n">
@@ -9451,13 +9463,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9484,7 +9496,7 @@
       <c r="I52" t="n">
         <v>-1.979999999999996</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K52" t="n">
@@ -9497,13 +9509,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9530,7 +9542,7 @@
       <c r="I53" t="n">
         <v>0.180000000000004</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K53" t="n">
@@ -9543,13 +9555,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9576,7 +9588,7 @@
       <c r="I54" t="n">
         <v>1.670000000000004</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9589,13 +9601,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9622,7 +9634,7 @@
       <c r="I55" t="n">
         <v>4.190000000000004</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="K55" t="n">
@@ -9635,13 +9647,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9668,7 +9680,7 @@
       <c r="I56" t="n">
         <v>5.350000000000004</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K56" t="n">
@@ -9681,13 +9693,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9714,7 +9726,7 @@
       <c r="I57" t="n">
         <v>7.900000000000004</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K57" t="n">
@@ -9727,13 +9739,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9760,7 +9772,7 @@
       <c r="I58" t="n">
         <v>9.540000000000004</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9773,13 +9785,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9806,7 +9818,7 @@
       <c r="I59" t="n">
         <v>9.120000000000003</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="K59" t="n">
@@ -9819,13 +9831,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9852,7 +9864,7 @@
       <c r="I60" t="n">
         <v>9.170000000000003</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="K60" t="n">
@@ -9865,13 +9877,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9898,7 +9910,7 @@
       <c r="I61" t="n">
         <v>7.310000000000003</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -9911,13 +9923,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9944,7 +9956,7 @@
       <c r="I62" t="n">
         <v>5.850000000000003</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="K62" t="n">
@@ -9957,13 +9969,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9990,7 +10002,7 @@
       <c r="I63" t="n">
         <v>5.840000000000003</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K63" t="n">
@@ -10003,13 +10015,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10036,7 +10048,7 @@
       <c r="I64" t="n">
         <v>5.250000000000004</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10049,13 +10061,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10082,7 +10094,7 @@
       <c r="I65" t="n">
         <v>5.520000000000004</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10095,13 +10107,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10128,7 +10140,7 @@
       <c r="I66" t="n">
         <v>5.400000000000004</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K66" t="n">
@@ -10141,13 +10153,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10174,7 +10186,7 @@
       <c r="I67" t="n">
         <v>4.560000000000003</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K67" t="n">
@@ -10187,13 +10199,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10220,7 +10232,7 @@
       <c r="I68" t="n">
         <v>4.390000000000003</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10233,13 +10245,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10266,7 +10278,7 @@
       <c r="I69" t="n">
         <v>4.460000000000004</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K69" t="n">
@@ -10279,13 +10291,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10312,7 +10324,7 @@
       <c r="I70" t="n">
         <v>4.250000000000004</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K70" t="n">
@@ -10325,13 +10337,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10358,7 +10370,7 @@
       <c r="I71" t="n">
         <v>4.170000000000003</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="K71" t="n">
@@ -10371,13 +10383,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10404,7 +10416,7 @@
       <c r="I72" t="n">
         <v>3.590000000000004</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10417,13 +10429,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10450,7 +10462,7 @@
       <c r="I73" t="n">
         <v>4.210000000000004</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10487,52 +10499,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="C2" t="n">
@@ -10561,10 +10573,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40119</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10593,10 +10605,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40224</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10625,10 +10637,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10657,10 +10669,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10689,10 +10701,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40479</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="C7" t="n">
@@ -10721,10 +10733,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40584</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10753,10 +10765,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40658</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C9" t="n">
@@ -10785,10 +10797,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40746</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10817,10 +10829,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40837</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="C11" t="n">
@@ -10849,10 +10861,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40948</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10881,10 +10893,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41017</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C13" t="n">
@@ -10913,10 +10925,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41108</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C14" t="n">
@@ -10945,10 +10957,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41206</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C15" t="n">
@@ -10977,10 +10989,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41311</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C16" t="n">
@@ -11009,10 +11021,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41388</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C17" t="n">
@@ -11041,10 +11053,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41473</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C18" t="n">
@@ -11073,10 +11085,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41569</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C19" t="n">
@@ -11105,10 +11117,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41682</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C20" t="n">
@@ -11137,10 +11149,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41752</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="C21" t="n">
@@ -11169,10 +11181,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41843</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C22" t="n">
@@ -11201,10 +11213,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41934</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C23" t="n">
@@ -11233,10 +11245,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42046</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C24" t="n">
@@ -11265,10 +11277,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42116</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11297,10 +11309,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42207</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11329,10 +11341,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42298</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11361,10 +11373,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42410</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42417</v>
       </c>
       <c r="C28" t="n">
@@ -11393,10 +11405,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11425,10 +11437,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42571</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11457,10 +11469,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42662</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C31" t="n">
@@ -11489,10 +11501,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42774</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="C32" t="n">
@@ -11521,10 +11533,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42844</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11553,10 +11565,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42935</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11585,10 +11597,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43026</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11617,10 +11629,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43138</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="C36" t="n">
@@ -11649,10 +11661,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43208</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11681,10 +11693,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43299</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C38" t="n">
@@ -11713,10 +11725,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43390</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C39" t="n">
@@ -11745,10 +11757,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43502</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="C40" t="n">
@@ -11777,10 +11789,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43572</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11809,10 +11821,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43670</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C42" t="n">
@@ -11841,10 +11853,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43761</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C43" t="n">
@@ -11873,10 +11885,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43866</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="C44" t="n">
@@ -11905,10 +11917,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43943</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -11937,10 +11949,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44034</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -11969,10 +11981,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44125</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12001,10 +12013,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44230</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="C48" t="n">
@@ -12033,10 +12045,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44307</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -12065,10 +12077,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44398</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12097,10 +12109,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44489</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12129,10 +12141,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44594</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="C52" t="n">
@@ -12161,10 +12173,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44671</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C53" t="n">
@@ -12193,10 +12205,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44762</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C54" t="n">
@@ -12225,10 +12237,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44853</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12257,10 +12269,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="C56" t="n">
@@ -12289,10 +12301,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45042</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="C57" t="n">
@@ -12321,10 +12333,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45126</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12353,10 +12365,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45224</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="C59" t="n">
@@ -12385,10 +12397,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45336</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C60" t="n">
@@ -12417,10 +12429,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45400</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12449,10 +12461,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C62" t="n">
@@ -12481,10 +12493,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C63" t="n">
@@ -12513,10 +12525,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45693</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="C64" t="n">
@@ -12545,10 +12557,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45770</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C65" t="n">
@@ -12577,10 +12589,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C66" t="n">
@@ -12609,10 +12621,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45953</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C67" t="n">
@@ -12641,10 +12653,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46057</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C68" t="n">
@@ -12673,10 +12685,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C69" t="n">
@@ -12705,10 +12717,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C70" t="n">
@@ -12737,10 +12749,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46225</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C71" t="n">
@@ -12787,12 +12799,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12863,7 +12875,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/DVN.xlsx
+++ b/salidas/empresas/DVN.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>41.41629791259766</v>
+        <v>41.41631317138672</v>
       </c>
       <c r="C2" t="n">
         <v>68.20999908447266</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.59944915771484</v>
+        <v>35.59945297241211</v>
       </c>
       <c r="C3" t="n">
         <v>58.63000106811523</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.21569442749023</v>
+        <v>37.21569061279297</v>
       </c>
       <c r="C4" t="n">
         <v>61.16999816894531</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>36.57081604003906</v>
+        <v>36.57080841064453</v>
       </c>
       <c r="C5" t="n">
         <v>60.11000061035156</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>36.83349990844727</v>
+        <v>36.83351516723633</v>
       </c>
       <c r="C7" t="n">
         <v>60.40999984741211</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>39.41263961791992</v>
+        <v>39.41263580322266</v>
       </c>
       <c r="C8" t="n">
         <v>64.63999938964844</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.10174942016602</v>
+        <v>38.10172653198242</v>
       </c>
       <c r="C9" t="n">
         <v>62.4900016784668</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>38.57099914550781</v>
+        <v>38.57099151611328</v>
       </c>
       <c r="C10" t="n">
         <v>63.15000152587891</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>40.82479476928711</v>
+        <v>40.82479858398438</v>
       </c>
       <c r="C11" t="n">
         <v>66.83999633789062</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>44.81321716308594</v>
+        <v>44.81322479248047</v>
       </c>
       <c r="C12" t="n">
         <v>73.37000274658203</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>41.03670120239258</v>
+        <v>41.03668212890625</v>
       </c>
       <c r="C13" t="n">
         <v>67.08000183105469</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.87807083129883</v>
+        <v>42.87808609008789</v>
       </c>
       <c r="C14" t="n">
         <v>70.08999633789062</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>40.19246673583984</v>
+        <v>40.19245529174805</v>
       </c>
       <c r="C15" t="n">
         <v>65.69999694824219</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.43818664550781</v>
+        <v>42.43817138671875</v>
       </c>
       <c r="C16" t="n">
         <v>69.22000122070312</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.67597961425781</v>
+        <v>44.67595672607422</v>
       </c>
       <c r="C17" t="n">
         <v>72.87000274658203</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>47.07314300537109</v>
+        <v>47.07316207885742</v>
       </c>
       <c r="C18" t="n">
         <v>76.77999877929688</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>48.08499526977539</v>
+        <v>48.08499908447266</v>
       </c>
       <c r="C19" t="n">
         <v>78.29000091552734</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>45.82477951049805</v>
+        <v>45.82477569580078</v>
       </c>
       <c r="C20" t="n">
         <v>74.61000061035156</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>46.25469207763672</v>
+        <v>46.25469970703125</v>
       </c>
       <c r="C21" t="n">
         <v>75.30999755859375</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>51.1919059753418</v>
+        <v>51.19191360473633</v>
       </c>
       <c r="C22" t="n">
         <v>83.19999694824219</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>57.46783828735352</v>
+        <v>57.46785354614258</v>
       </c>
       <c r="C23" t="n">
         <v>93.40000152587891</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>50.95195770263672</v>
+        <v>50.95192337036133</v>
       </c>
       <c r="C24" t="n">
         <v>82.80999755859375</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>54.79338836669922</v>
+        <v>54.79341506958008</v>
       </c>
       <c r="C25" t="n">
         <v>88.91000366210938</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>52.41460037231445</v>
+        <v>52.41457748413086</v>
       </c>
       <c r="C26" t="n">
         <v>85.05000305175781</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>63.30423355102539</v>
+        <v>63.30422592163086</v>
       </c>
       <c r="C27" t="n">
         <v>102.7200012207031</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>64.4967041015625</v>
+        <v>64.49669647216797</v>
       </c>
       <c r="C28" t="n">
         <v>104.3300018310547</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>70.10377502441406</v>
+        <v>70.103759765625</v>
       </c>
       <c r="C29" t="n">
         <v>113.4000015258789</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>71.67398834228516</v>
+        <v>71.67400360107422</v>
       </c>
       <c r="C30" t="n">
         <v>115.9400024414062</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>74.38486480712891</v>
+        <v>74.38484191894531</v>
       </c>
       <c r="C31" t="n">
         <v>120.1600036621094</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>58.74152374267578</v>
+        <v>58.74153518676758</v>
       </c>
       <c r="C32" t="n">
         <v>94.88999938964844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>63.17389678955078</v>
+        <v>63.17388534545898</v>
       </c>
       <c r="C33" t="n">
         <v>102.0500030517578</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>56.55510711669922</v>
+        <v>56.55513381958008</v>
       </c>
       <c r="C34" t="n">
         <v>91.19999694824219</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>50.1430549621582</v>
+        <v>50.14304733276367</v>
       </c>
       <c r="C35" t="n">
         <v>80.86000061035156</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>44.85962295532227</v>
+        <v>44.8596076965332</v>
       </c>
       <c r="C36" t="n">
         <v>72.33999633789062</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>40.83826446533203</v>
+        <v>40.8382568359375</v>
       </c>
       <c r="C37" t="n">
         <v>65.70999908447266</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>38.28393173217773</v>
+        <v>38.28392791748047</v>
       </c>
       <c r="C38" t="n">
         <v>61.59999847412109</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>27.14057159423828</v>
+        <v>27.14056015014648</v>
       </c>
       <c r="C39" t="n">
         <v>43.66999816894531</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.87995338439941</v>
+        <v>27.87993049621582</v>
       </c>
       <c r="C40" t="n">
         <v>44.68999862670898</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.34674835205078</v>
+        <v>32.34672546386719</v>
       </c>
       <c r="C41" t="n">
         <v>51.84999847412109</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>39.45241546630859</v>
+        <v>39.45241165161133</v>
       </c>
       <c r="C42" t="n">
         <v>63.2400016784668</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>34.08549118041992</v>
+        <v>34.08547592163086</v>
       </c>
       <c r="C43" t="n">
         <v>54.5</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>36.33074188232422</v>
+        <v>36.33073043823242</v>
       </c>
       <c r="C44" t="n">
         <v>58.09000015258789</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>38.38838195800781</v>
+        <v>38.38839340209961</v>
       </c>
       <c r="C45" t="n">
         <v>61.38000106811523</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>42.21286773681641</v>
+        <v>42.21287155151367</v>
       </c>
       <c r="C46" t="n">
         <v>67.33000183105469</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>40.57025909423828</v>
+        <v>40.57024765014648</v>
       </c>
       <c r="C47" t="n">
         <v>64.70999908447266</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>42.22539901733398</v>
+        <v>42.22542190551758</v>
       </c>
       <c r="C48" t="n">
         <v>67.34999847412109</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>46.19659805297852</v>
+        <v>46.19660186767578</v>
       </c>
       <c r="C49" t="n">
         <v>73.5</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.05462646484375</v>
+        <v>42.05461883544922</v>
       </c>
       <c r="C50" t="n">
         <v>66.91000366210938</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>43.28025436401367</v>
+        <v>43.28025817871094</v>
       </c>
       <c r="C51" t="n">
         <v>68.86000061035156</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>40.58625030517578</v>
+        <v>40.58625411987305</v>
       </c>
       <c r="C52" t="n">
         <v>64.43000030517578</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>42.41305923461914</v>
+        <v>42.41304397583008</v>
       </c>
       <c r="C53" t="n">
         <v>67.33000183105469</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>40.22089767456055</v>
+        <v>40.22089385986328</v>
       </c>
       <c r="C54" t="n">
         <v>63.84999847412109</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>38.46595001220703</v>
+        <v>38.4659309387207</v>
       </c>
       <c r="C55" t="n">
         <v>60.91999816894531</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.45726776123047</v>
+        <v>39.45728302001953</v>
       </c>
       <c r="C56" t="n">
         <v>62.4900016784668</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>38.06183624267578</v>
+        <v>38.06184387207031</v>
       </c>
       <c r="C57" t="n">
         <v>60.27999877929688</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>40.98282241821289</v>
+        <v>40.98281860351562</v>
       </c>
       <c r="C58" t="n">
         <v>64.73999786376953</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>41.16008377075195</v>
+        <v>41.16007232666016</v>
       </c>
       <c r="C59" t="n">
         <v>65.01999664306641</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>44.67343521118164</v>
+        <v>44.67344284057617</v>
       </c>
       <c r="C60" t="n">
         <v>70.56999969482422</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>49.80847930908203</v>
+        <v>49.80849838256836</v>
       </c>
       <c r="C61" t="n">
         <v>78.51000213623047</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>56.26690673828125</v>
+        <v>56.26691818237305</v>
       </c>
       <c r="C62" t="n">
         <v>88.69000244140625</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>58.01158142089844</v>
+        <v>58.01156997680664</v>
       </c>
       <c r="C63" t="n">
         <v>91.44000244140625</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>58.32931900024414</v>
+        <v>58.32934951782227</v>
       </c>
       <c r="C64" t="n">
         <v>91.76999664306641</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>57.83990859985352</v>
+        <v>57.83993148803711</v>
       </c>
       <c r="C65" t="n">
         <v>91</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>53.4351921081543</v>
+        <v>53.4351806640625</v>
       </c>
       <c r="C66" t="n">
         <v>84.06999969482422</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>50.19922256469727</v>
+        <v>50.19921875</v>
       </c>
       <c r="C67" t="n">
         <v>78.80999755859375</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>50.129150390625</v>
+        <v>50.12915420532227</v>
       </c>
       <c r="C68" t="n">
         <v>78.69999694824219</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>43.20533752441406</v>
+        <v>43.20534515380859</v>
       </c>
       <c r="C69" t="n">
         <v>67.83000183105469</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.48145294189453</v>
+        <v>41.48144912719727</v>
       </c>
       <c r="C71" t="n">
         <v>64.94999694824219</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>41.80717849731445</v>
+        <v>41.80717468261719</v>
       </c>
       <c r="C72" t="n">
         <v>65.45999908447266</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>40.86151504516602</v>
+        <v>40.86152648925781</v>
       </c>
       <c r="C74" t="n">
         <v>63.81000137329102</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>46.94495391845703</v>
+        <v>46.94496536254883</v>
       </c>
       <c r="C75" t="n">
         <v>73.30999755859375</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>45.67102432250977</v>
+        <v>45.67101669311523</v>
       </c>
       <c r="C76" t="n">
         <v>71.12000274658203</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>44.85546875</v>
+        <v>44.85546112060547</v>
       </c>
       <c r="C77" t="n">
         <v>69.84999847412109</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>38.22187042236328</v>
+        <v>38.22186279296875</v>
       </c>
       <c r="C78" t="n">
         <v>59.52000045776367</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>37.36921691894531</v>
+        <v>37.36920547485352</v>
       </c>
       <c r="C79" t="n">
         <v>57.9900016784668</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>38.09739303588867</v>
+        <v>38.09739685058594</v>
       </c>
       <c r="C80" t="n">
         <v>59.11999893188477</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>37.26611328125</v>
+        <v>37.26611709594727</v>
       </c>
       <c r="C81" t="n">
         <v>57.83000183105469</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>33.40676498413086</v>
+        <v>33.40678024291992</v>
       </c>
       <c r="C84" t="n">
         <v>51.66999816894531</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>33.77476119995117</v>
+        <v>33.77474594116211</v>
       </c>
       <c r="C85" t="n">
         <v>52.04000091552734</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>37.1171875</v>
+        <v>37.11717987060547</v>
       </c>
       <c r="C86" t="n">
         <v>57.18999862670898</v>
@@ -2515,7 +2515,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>35.86318588256836</v>
+        <v>35.86318969726562</v>
       </c>
       <c r="C89" t="n">
         <v>55.06000137329102</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>37.02909851074219</v>
+        <v>37.02910232543945</v>
       </c>
       <c r="C90" t="n">
         <v>56.84999847412109</v>
@@ -2569,7 +2569,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>33.92696762084961</v>
+        <v>33.92698287963867</v>
       </c>
       <c r="C91" t="n">
         <v>51.88000106811523</v>
@@ -2596,7 +2596,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>35.97383880615234</v>
+        <v>35.97384643554688</v>
       </c>
       <c r="C92" t="n">
         <v>55.0099983215332</v>
@@ -2623,7 +2623,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.33406066894531</v>
+        <v>37.33404159545898</v>
       </c>
       <c r="C93" t="n">
         <v>57.09000015258789</v>
@@ -2650,7 +2650,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>37.9142951965332</v>
+        <v>37.914306640625</v>
       </c>
       <c r="C94" t="n">
         <v>57.7599983215332</v>
@@ -2677,7 +2677,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>41.49831390380859</v>
+        <v>41.49832534790039</v>
       </c>
       <c r="C95" t="n">
         <v>63.22000122070312</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>39.79162216186523</v>
+        <v>39.79163360595703</v>
       </c>
       <c r="C96" t="n">
         <v>60.61999893188477</v>
@@ -2731,7 +2731,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>40.75959014892578</v>
+        <v>40.75959396362305</v>
       </c>
       <c r="C97" t="n">
         <v>61.86999893188477</v>
@@ -2758,7 +2758,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>39.0137939453125</v>
+        <v>39.01379013061523</v>
       </c>
       <c r="C98" t="n">
         <v>59.22000122070312</v>
@@ -2785,7 +2785,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>42.43949890136719</v>
+        <v>42.43950653076172</v>
       </c>
       <c r="C99" t="n">
         <v>64.41999816894531</v>
@@ -2839,7 +2839,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>46.27579498291016</v>
+        <v>46.27578735351562</v>
       </c>
       <c r="C101" t="n">
         <v>70</v>
@@ -2866,7 +2866,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.85400009155273</v>
+        <v>48.85400772094727</v>
       </c>
       <c r="C102" t="n">
         <v>73.90000152587891</v>
@@ -2924,7 +2924,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>50.07209396362305</v>
+        <v>50.07210159301758</v>
       </c>
       <c r="C104" t="n">
         <v>75.5</v>
@@ -2953,7 +2953,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>50.01903533935547</v>
+        <v>50.0190315246582</v>
       </c>
       <c r="C105" t="n">
         <v>75.41999816894531</v>
@@ -2982,7 +2982,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.37134170532227</v>
+        <v>45.371337890625</v>
       </c>
       <c r="C106" t="n">
         <v>68.18000030517578</v>
@@ -3040,7 +3040,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.24240875244141</v>
+        <v>39.24241638183594</v>
       </c>
       <c r="C108" t="n">
         <v>58.97000122070312</v>
@@ -3069,7 +3069,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>40.90468597412109</v>
+        <v>40.90467071533203</v>
       </c>
       <c r="C109" t="n">
         <v>61.20999908447266</v>
@@ -3098,7 +3098,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>40.27651214599609</v>
+        <v>40.2765007019043</v>
       </c>
       <c r="C110" t="n">
         <v>60.27000045776367</v>
@@ -3127,7 +3127,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>41.15861511230469</v>
+        <v>41.15861892700195</v>
       </c>
       <c r="C111" t="n">
         <v>61.59000015258789</v>
@@ -3156,7 +3156,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>40.47367858886719</v>
+        <v>40.47369766235352</v>
       </c>
       <c r="C112" t="n">
         <v>60.31000137329102</v>
@@ -3185,7 +3185,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>45.77531814575195</v>
+        <v>45.77532577514648</v>
       </c>
       <c r="C113" t="n">
         <v>68.20999908447266</v>
@@ -3214,7 +3214,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>43.76876068115234</v>
+        <v>43.76875686645508</v>
       </c>
       <c r="C114" t="n">
         <v>65.22000122070312</v>
@@ -3241,7 +3241,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.07411193847656</v>
+        <v>40.07411575317383</v>
       </c>
       <c r="C115" t="n">
         <v>59.4900016784668</v>
@@ -3295,7 +3295,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>28.73696136474609</v>
+        <v>28.73695373535156</v>
       </c>
       <c r="C117" t="n">
         <v>42.65999984741211</v>
@@ -3322,7 +3322,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>25.13569831848145</v>
+        <v>25.13570213317871</v>
       </c>
       <c r="C118" t="n">
         <v>37.09000015258789</v>
@@ -3349,7 +3349,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>28.41574096679688</v>
+        <v>28.41574478149414</v>
       </c>
       <c r="C119" t="n">
         <v>41.93000030517578</v>
@@ -3376,7 +3376,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.18072891235352</v>
+        <v>31.18073463439941</v>
       </c>
       <c r="C120" t="n">
         <v>46.0099983215332</v>
@@ -3403,7 +3403,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>21.83380317687988</v>
+        <v>21.83380126953125</v>
       </c>
       <c r="C121" t="n">
         <v>32</v>
@@ -3484,7 +3484,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>18.92452621459961</v>
+        <v>18.92452239990234</v>
       </c>
       <c r="C124" t="n">
         <v>27.44000053405762</v>
@@ -3565,7 +3565,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.04329681396484</v>
+        <v>25.04329490661621</v>
       </c>
       <c r="C127" t="n">
         <v>36.25</v>
@@ -3592,7 +3592,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>26.44571876525879</v>
+        <v>26.44572257995605</v>
       </c>
       <c r="C128" t="n">
         <v>38.27999877929688</v>
@@ -3619,7 +3619,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.93451118469238</v>
+        <v>29.93450927734375</v>
       </c>
       <c r="C129" t="n">
         <v>43.33000183105469</v>
@@ -3646,7 +3646,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>30.51577377319336</v>
+        <v>30.51577186584473</v>
       </c>
       <c r="C130" t="n">
         <v>44.11000061035156</v>
@@ -3673,7 +3673,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>26.21270179748535</v>
+        <v>26.21270561218262</v>
       </c>
       <c r="C131" t="n">
         <v>37.88999938964844</v>
@@ -3700,7 +3700,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>33.43521499633789</v>
+        <v>33.43520355224609</v>
       </c>
       <c r="C132" t="n">
         <v>48.33000183105469</v>
@@ -3727,7 +3727,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>31.63443756103516</v>
+        <v>31.63443946838379</v>
       </c>
       <c r="C133" t="n">
         <v>45.66999816894531</v>
@@ -3754,7 +3754,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>31.54439163208008</v>
+        <v>31.54438018798828</v>
       </c>
       <c r="C134" t="n">
         <v>45.54000091552734</v>
@@ -3781,7 +3781,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>30.03436088562012</v>
+        <v>30.03435325622559</v>
       </c>
       <c r="C135" t="n">
         <v>43.36000061035156</v>
@@ -3835,7 +3835,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>27.39453506469727</v>
+        <v>27.3945369720459</v>
       </c>
       <c r="C137" t="n">
         <v>39.4900016784668</v>
@@ -3862,7 +3862,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>23.57220268249512</v>
+        <v>23.57220077514648</v>
       </c>
       <c r="C138" t="n">
         <v>33.97999954223633</v>
@@ -3920,7 +3920,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>23.14986801147461</v>
+        <v>23.14987182617188</v>
       </c>
       <c r="C140" t="n">
         <v>33.31000137329102</v>
@@ -3949,7 +3949,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>21.82245445251465</v>
+        <v>21.82245254516602</v>
       </c>
       <c r="C141" t="n">
         <v>31.39999961853027</v>
@@ -3978,7 +3978,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>25.55856704711914</v>
+        <v>25.55857467651367</v>
       </c>
       <c r="C142" t="n">
         <v>36.70999908447266</v>
@@ -4007,7 +4007,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>25.69086456298828</v>
+        <v>25.69085502624512</v>
       </c>
       <c r="C143" t="n">
         <v>36.90000152587891</v>
@@ -4036,7 +4036,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>26.82571029663086</v>
+        <v>26.82571411132812</v>
       </c>
       <c r="C144" t="n">
         <v>38.52999877929688</v>
@@ -4065,7 +4065,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>28.86932373046875</v>
+        <v>28.86932563781738</v>
       </c>
       <c r="C145" t="n">
         <v>41.40000152587891</v>
@@ -4094,7 +4094,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>28.84840202331543</v>
+        <v>28.8484058380127</v>
       </c>
       <c r="C146" t="n">
         <v>41.36999893188477</v>
@@ -4123,7 +4123,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>21.38701438903809</v>
+        <v>21.38701057434082</v>
       </c>
       <c r="C147" t="n">
         <v>30.67000007629395</v>
@@ -4152,7 +4152,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>22.20866203308105</v>
+        <v>22.20865631103516</v>
       </c>
       <c r="C148" t="n">
         <v>31.79000091552734</v>
@@ -4181,7 +4181,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>25.38032341003418</v>
+        <v>25.38031387329102</v>
       </c>
       <c r="C149" t="n">
         <v>36.33000183105469</v>
@@ -4210,7 +4210,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>29.041015625</v>
+        <v>29.04101371765137</v>
       </c>
       <c r="C150" t="n">
         <v>41.56999969482422</v>
@@ -4268,7 +4268,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>31.50338745117188</v>
+        <v>31.50338935852051</v>
       </c>
       <c r="C152" t="n">
         <v>45.0099983215332</v>
@@ -4297,7 +4297,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>30.04755020141602</v>
+        <v>30.04755783081055</v>
       </c>
       <c r="C153" t="n">
         <v>42.93000030517578</v>
@@ -4324,7 +4324,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>28.00821113586426</v>
+        <v>28.00821304321289</v>
       </c>
       <c r="C154" t="n">
         <v>39.93999862670898</v>
@@ -4351,7 +4351,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>22.72073554992676</v>
+        <v>22.72072982788086</v>
       </c>
       <c r="C155" t="n">
         <v>32.40000152587891</v>
@@ -4407,7 +4407,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>15.85282516479492</v>
+        <v>15.85282707214355</v>
       </c>
       <c r="C157" t="n">
         <v>22.54000091552734</v>
@@ -4436,7 +4436,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>18.74347114562988</v>
+        <v>18.74346733093262</v>
       </c>
       <c r="C158" t="n">
         <v>26.64999961853027</v>
@@ -4465,7 +4465,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>20.75496482849121</v>
+        <v>20.75496292114258</v>
       </c>
       <c r="C159" t="n">
         <v>29.51000022888184</v>
@@ -4494,7 +4494,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>22.25747299194336</v>
+        <v>22.25747489929199</v>
       </c>
       <c r="C160" t="n">
         <v>31.55999946594238</v>
@@ -4523,7 +4523,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>22.66651344299316</v>
+        <v>22.6665153503418</v>
       </c>
       <c r="C161" t="n">
         <v>32.13999938964844</v>
@@ -4552,7 +4552,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>17.74392127990723</v>
+        <v>17.74392318725586</v>
       </c>
       <c r="C162" t="n">
         <v>25.15999984741211</v>
@@ -4581,7 +4581,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>20.18483352661133</v>
+        <v>20.18482780456543</v>
       </c>
       <c r="C163" t="n">
         <v>28.52000045776367</v>
@@ -4639,7 +4639,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>15.56327342987061</v>
+        <v>15.56327438354492</v>
       </c>
       <c r="C165" t="n">
         <v>21.98999977111816</v>
@@ -4668,7 +4668,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>17.08990097045898</v>
+        <v>17.08989334106445</v>
       </c>
       <c r="C166" t="n">
         <v>24.05999946594238</v>
@@ -4726,7 +4726,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>15.54853534698486</v>
+        <v>15.54854011535645</v>
       </c>
       <c r="C168" t="n">
         <v>21.88999938964844</v>
@@ -4755,7 +4755,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>18.51773452758789</v>
+        <v>18.51773834228516</v>
       </c>
       <c r="C169" t="n">
         <v>25.96999931335449</v>
@@ -4784,7 +4784,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>15.48730182647705</v>
+        <v>15.4873046875</v>
       </c>
       <c r="C170" t="n">
         <v>21.71999931335449</v>
@@ -4840,7 +4840,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>4.980428695678711</v>
+        <v>4.980428218841553</v>
       </c>
       <c r="C172" t="n">
         <v>6.909999847412109</v>
@@ -4867,7 +4867,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>8.987834930419922</v>
+        <v>8.987835884094238</v>
       </c>
       <c r="C173" t="n">
         <v>12.47000026702881</v>
@@ -4894,7 +4894,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>7.791380882263184</v>
+        <v>7.791379928588867</v>
       </c>
       <c r="C174" t="n">
         <v>10.8100004196167</v>
@@ -4948,7 +4948,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>7.629529476165771</v>
+        <v>7.629527568817139</v>
       </c>
       <c r="C176" t="n">
         <v>10.48999977111816</v>
@@ -4975,7 +4975,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>8.07370662689209</v>
+        <v>8.073707580566406</v>
       </c>
       <c r="C177" t="n">
         <v>10.86999988555908</v>
@@ -5056,7 +5056,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>10.52157115936279</v>
+        <v>10.52157402038574</v>
       </c>
       <c r="C180" t="n">
         <v>13.98999977111816</v>
@@ -5083,7 +5083,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>11.974196434021</v>
+        <v>11.97419738769531</v>
       </c>
       <c r="C181" t="n">
         <v>15.8100004196167</v>
@@ -5137,7 +5137,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>16.31398963928223</v>
+        <v>16.31399345397949</v>
       </c>
       <c r="C183" t="n">
         <v>21.54000091552734</v>
@@ -5218,7 +5218,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>20.36397552490234</v>
+        <v>20.36397743225098</v>
       </c>
       <c r="C186" t="n">
         <v>26.55999946594238</v>
@@ -5245,7 +5245,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>22.64238548278809</v>
+        <v>22.64238166809082</v>
       </c>
       <c r="C187" t="n">
         <v>29.19000053405762</v>
@@ -5272,7 +5272,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>20.0438289642334</v>
+        <v>20.04382705688477</v>
       </c>
       <c r="C188" t="n">
         <v>25.84000015258789</v>
@@ -5299,7 +5299,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>22.921630859375</v>
+        <v>22.92163467407227</v>
       </c>
       <c r="C189" t="n">
         <v>29.54999923706055</v>
@@ -5328,7 +5328,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>28.02746200561523</v>
+        <v>28.02746391296387</v>
       </c>
       <c r="C190" t="n">
         <v>35.5099983215332</v>
@@ -5357,7 +5357,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.63449668884277</v>
+        <v>31.63448715209961</v>
       </c>
       <c r="C191" t="n">
         <v>40.08000183105469</v>
@@ -5386,7 +5386,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>33.1972770690918</v>
+        <v>33.19727325439453</v>
       </c>
       <c r="C192" t="n">
         <v>42.06000137329102</v>
@@ -5415,7 +5415,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>35.43064498901367</v>
+        <v>35.43064117431641</v>
       </c>
       <c r="C193" t="n">
         <v>44.04999923706055</v>
@@ -5473,7 +5473,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>47.89772415161133</v>
+        <v>47.89773178100586</v>
       </c>
       <c r="C195" t="n">
         <v>59.54999923706055</v>
@@ -5531,7 +5531,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>47.57318496704102</v>
+        <v>47.57317733764648</v>
       </c>
       <c r="C197" t="n">
         <v>58.16999816894531</v>
@@ -5560,7 +5560,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>61.2554817199707</v>
+        <v>61.25548934936523</v>
       </c>
       <c r="C198" t="n">
         <v>74.90000152587891</v>
@@ -5647,7 +5647,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>58.71298217773438</v>
+        <v>58.71297454833984</v>
       </c>
       <c r="C201" t="n">
         <v>70.62000274658203</v>
@@ -5676,7 +5676,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>51.14200210571289</v>
+        <v>51.14200973510742</v>
       </c>
       <c r="C202" t="n">
         <v>60.13000106811523</v>
@@ -5705,7 +5705,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>65.78803253173828</v>
+        <v>65.78804016113281</v>
       </c>
       <c r="C203" t="n">
         <v>77.34999847412109</v>
@@ -5734,7 +5734,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>58.27790832519531</v>
+        <v>58.27789306640625</v>
       </c>
       <c r="C204" t="n">
         <v>68.51999664306641</v>
@@ -5763,7 +5763,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>53.45212173461914</v>
+        <v>53.45210647583008</v>
       </c>
       <c r="C205" t="n">
         <v>61.5099983215332</v>
@@ -5792,7 +5792,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>54.95548248291016</v>
+        <v>54.95548629760742</v>
       </c>
       <c r="C206" t="n">
         <v>63.2400016784668</v>
@@ -5821,7 +5821,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.85641098022461</v>
+        <v>46.85641479492188</v>
       </c>
       <c r="C207" t="n">
         <v>53.91999816894531</v>
@@ -5850,7 +5850,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>44.77738571166992</v>
+        <v>44.77739334106445</v>
       </c>
       <c r="C208" t="n">
         <v>50.61000061035156</v>
@@ -5879,7 +5879,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>47.27239227294922</v>
+        <v>47.27239990234375</v>
       </c>
       <c r="C209" t="n">
         <v>53.43000030517578</v>
@@ -5908,7 +5908,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>40.78715515136719</v>
+        <v>40.78714752197266</v>
       </c>
       <c r="C210" t="n">
         <v>46.09999847412109</v>
@@ -5937,7 +5937,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>43.38896942138672</v>
+        <v>43.38895797729492</v>
       </c>
       <c r="C211" t="n">
         <v>48.34000015258789</v>
@@ -5966,7 +5966,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>48.46925354003906</v>
+        <v>48.46925735473633</v>
       </c>
       <c r="C212" t="n">
         <v>54</v>
@@ -5995,7 +5995,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>45.85730361938477</v>
+        <v>45.8572998046875</v>
       </c>
       <c r="C213" t="n">
         <v>51.09000015258789</v>
@@ -6053,7 +6053,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>42.20858001708984</v>
+        <v>42.20858383178711</v>
       </c>
       <c r="C215" t="n">
         <v>46.56999969482422</v>
@@ -6082,7 +6082,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>40.75843048095703</v>
+        <v>40.75842666625977</v>
       </c>
       <c r="C216" t="n">
         <v>44.97000122070312</v>
@@ -6140,7 +6140,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>38.75962066650391</v>
+        <v>38.75962829589844</v>
       </c>
       <c r="C218" t="n">
         <v>42.02000045776367</v>
@@ -6169,7 +6169,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>40.64134216308594</v>
+        <v>40.64133453369141</v>
       </c>
       <c r="C219" t="n">
         <v>44.06000137329102</v>
@@ -6198,7 +6198,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>46.72006988525391</v>
+        <v>46.72007369995117</v>
       </c>
       <c r="C220" t="n">
         <v>50.18000030517578</v>
@@ -6227,7 +6227,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>47.65113067626953</v>
+        <v>47.65112686157227</v>
       </c>
       <c r="C221" t="n">
         <v>51.18000030517578</v>
@@ -6256,7 +6256,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>45.69591522216797</v>
+        <v>45.6959228515625</v>
       </c>
       <c r="C222" t="n">
         <v>49.08000183105469</v>
@@ -6314,7 +6314,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>44.12475967407227</v>
+        <v>44.124755859375</v>
       </c>
       <c r="C224" t="n">
         <v>47.02999877929688</v>
@@ -6343,7 +6343,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>42.01375198364258</v>
+        <v>42.01375579833984</v>
       </c>
       <c r="C225" t="n">
         <v>44.77999877929688</v>
@@ -6372,7 +6372,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>37.11151504516602</v>
+        <v>37.11151885986328</v>
       </c>
       <c r="C226" t="n">
         <v>39.11999893188477</v>
@@ -6430,7 +6430,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>36.0015869140625</v>
+        <v>36.00159454345703</v>
       </c>
       <c r="C228" t="n">
         <v>37.95000076293945</v>
@@ -6459,7 +6459,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>31.25103378295898</v>
+        <v>31.25103187561035</v>
       </c>
       <c r="C229" t="n">
         <v>32.72999954223633</v>
@@ -6488,7 +6488,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>32.55912399291992</v>
+        <v>32.55913162231445</v>
       </c>
       <c r="C230" t="n">
         <v>34.09999847412109</v>
@@ -6517,7 +6517,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>34.58333969116211</v>
+        <v>34.58333587646484</v>
       </c>
       <c r="C231" t="n">
         <v>36.22000122070312</v>
@@ -6546,7 +6546,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>35.96546173095703</v>
+        <v>35.9654655456543</v>
       </c>
       <c r="C232" t="n">
         <v>37.40000152587891</v>
@@ -6575,7 +6575,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>29.24357223510742</v>
+        <v>29.24357414245605</v>
       </c>
       <c r="C233" t="n">
         <v>30.40999984741211</v>
@@ -6604,7 +6604,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>29.09932899475098</v>
+        <v>29.09932708740234</v>
       </c>
       <c r="C234" t="n">
         <v>30.26000022888184</v>
@@ -6633,7 +6633,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>30.80523490905762</v>
+        <v>30.80523300170898</v>
       </c>
       <c r="C235" t="n">
         <v>31.80999946594238</v>
@@ -6662,7 +6662,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>32.17069625854492</v>
+        <v>32.17070388793945</v>
       </c>
       <c r="C236" t="n">
         <v>33.22000122070312</v>
@@ -6691,7 +6691,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>34.9597282409668</v>
+        <v>34.95972442626953</v>
       </c>
       <c r="C237" t="n">
         <v>36.09999847412109</v>
@@ -6720,7 +6720,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>34.18856811523438</v>
+        <v>34.18857192993164</v>
       </c>
       <c r="C238" t="n">
         <v>35.06000137329102</v>
@@ -6749,7 +6749,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>31.68244552612305</v>
+        <v>31.68244743347168</v>
       </c>
       <c r="C239" t="n">
         <v>32.4900016784668</v>
@@ -6865,7 +6865,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>42.72130966186523</v>
+        <v>42.72130584716797</v>
       </c>
       <c r="C243" t="n">
         <v>43.52999877929688</v>
